--- a/backend/data/financials_by_company/1PNE.MI.xlsx
+++ b/backend/data/financials_by_company/1PNE.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA5"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,646 +687,807 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>225000</v>
+        <v>929100</v>
       </c>
       <c r="C2" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>46400000</v>
+        <v>32377000</v>
       </c>
       <c r="E2" t="n">
-        <v>1500000</v>
+        <v>3123000</v>
       </c>
       <c r="F2" t="n">
-        <v>1500000</v>
+        <v>3097000</v>
       </c>
       <c r="G2" t="n">
-        <v>-13400000</v>
+        <v>25127000</v>
       </c>
       <c r="H2" t="n">
-        <v>31400000</v>
+        <v>23415000</v>
       </c>
       <c r="I2" t="n">
-        <v>55400000</v>
+        <v>36159000</v>
       </c>
       <c r="J2" t="n">
-        <v>47900000</v>
+        <v>35500000</v>
       </c>
       <c r="K2" t="n">
-        <v>14100000</v>
+        <v>12085000</v>
       </c>
       <c r="L2" t="n">
-        <v>-35300000</v>
+        <v>-9015000</v>
       </c>
       <c r="M2" t="n">
-        <v>16900000</v>
+        <v>9057000</v>
       </c>
       <c r="N2" t="n">
-        <v>10400000</v>
+        <v>884000</v>
       </c>
       <c r="O2" t="n">
-        <v>-14675000</v>
+        <v>22985100</v>
       </c>
       <c r="P2" t="n">
-        <v>-13400000</v>
+        <v>25127000</v>
       </c>
       <c r="Q2" t="n">
-        <v>178800000</v>
+        <v>108921000</v>
       </c>
       <c r="R2" t="n">
-        <v>2600000</v>
+        <v>1203000</v>
       </c>
       <c r="S2" t="n">
-        <v>35100000</v>
+        <v>9265000</v>
       </c>
       <c r="T2" t="n">
-        <v>76500000</v>
+        <v>76337000</v>
       </c>
       <c r="U2" t="n">
-        <v>76500000</v>
+        <v>76337000</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.18</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.18</v>
+        <v>0.33</v>
       </c>
       <c r="X2" t="n">
-        <v>-13400000</v>
+        <v>25127000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-13400000</v>
+        <v>25127000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-13400000</v>
+        <v>25127000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-700000</v>
+        <v>463000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-12700000</v>
+        <v>24664000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-12700000</v>
+        <v>24664000</v>
       </c>
       <c r="AF2" t="n">
-        <v>9900000</v>
+        <v>-21636000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2800000</v>
+        <v>3028000</v>
       </c>
       <c r="AH2" t="n">
-        <v>3500000</v>
+        <v>458000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3200000</v>
+        <v>-410000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-300000</v>
+        <v>-74000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-35300000</v>
+        <v>-9015000</v>
       </c>
       <c r="AL2" t="n">
-        <v>28800000</v>
+        <v>842000</v>
       </c>
       <c r="AM2" t="n">
-        <v>16900000</v>
+        <v>9057000</v>
       </c>
       <c r="AN2" t="n">
-        <v>10400000</v>
+        <v>884000</v>
       </c>
       <c r="AO2" t="n">
-        <v>31600000</v>
+        <v>8807000</v>
       </c>
       <c r="AP2" t="n">
-        <v>123400000</v>
+        <v>72762000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17500000</v>
+        <v>5192000</v>
       </c>
       <c r="AR2" t="n">
-        <v>33800000</v>
+        <v>23389000</v>
       </c>
       <c r="AS2" t="n">
-        <v>33800000</v>
+        <v>23389000</v>
       </c>
       <c r="AT2" t="n">
-        <v>15200000</v>
+        <v>7726000</v>
       </c>
       <c r="AU2" t="n">
-        <v>4300000</v>
+        <v>1622000</v>
       </c>
       <c r="AV2" t="n">
-        <v>10900000</v>
+        <v>6104000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2600000</v>
+        <v>1203000</v>
       </c>
       <c r="AX2" t="n">
-        <v>155000000</v>
+        <v>81569000</v>
       </c>
       <c r="AY2" t="n">
-        <v>55400000</v>
+        <v>36159000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>210400000</v>
+        <v>117728000</v>
       </c>
       <c r="BA2" t="n">
-        <v>210400000</v>
+        <v>117728000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>288372.093023</v>
+        <v>2672100</v>
       </c>
       <c r="C3" t="n">
-        <v>0.046512</v>
+        <v>0.15</v>
       </c>
       <c r="D3" t="n">
-        <v>34700000</v>
+        <v>47237000</v>
       </c>
       <c r="E3" t="n">
-        <v>6200000</v>
+        <v>17840000</v>
       </c>
       <c r="F3" t="n">
-        <v>6200000</v>
+        <v>17814000</v>
       </c>
       <c r="G3" t="n">
-        <v>-9600000</v>
+        <v>14903000</v>
       </c>
       <c r="H3" t="n">
-        <v>34200000</v>
+        <v>29371000</v>
       </c>
       <c r="I3" t="n">
-        <v>11900000</v>
+        <v>30813000</v>
       </c>
       <c r="J3" t="n">
-        <v>40900000</v>
+        <v>65077000</v>
       </c>
       <c r="K3" t="n">
-        <v>6700000</v>
+        <v>35706000</v>
       </c>
       <c r="L3" t="n">
-        <v>-19800000</v>
+        <v>1093000</v>
       </c>
       <c r="M3" t="n">
-        <v>15300000</v>
+        <v>11844000</v>
       </c>
       <c r="N3" t="n">
-        <v>2600000</v>
+        <v>16106000</v>
       </c>
       <c r="O3" t="n">
-        <v>-15511627.906977</v>
+        <v>-212900</v>
       </c>
       <c r="P3" t="n">
-        <v>-9600000</v>
+        <v>14903000</v>
       </c>
       <c r="Q3" t="n">
-        <v>116700000</v>
+        <v>121403000</v>
       </c>
       <c r="R3" t="n">
-        <v>2800000</v>
+        <v>3699000</v>
       </c>
       <c r="S3" t="n">
-        <v>5700000</v>
+        <v>6173000</v>
       </c>
       <c r="T3" t="n">
-        <v>76300000</v>
+        <v>76337000</v>
       </c>
       <c r="U3" t="n">
-        <v>76300000</v>
+        <v>76337000</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.13</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.13</v>
+        <v>0.2</v>
       </c>
       <c r="X3" t="n">
-        <v>-9600000</v>
+        <v>14903000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-9600000</v>
+        <v>14903000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-9600000</v>
+        <v>14903000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1400000</v>
+        <v>809000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-8200000</v>
+        <v>14094000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-8200000</v>
+        <v>14094000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-400000</v>
+        <v>9768000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-8600000</v>
+        <v>23862000</v>
       </c>
       <c r="AH3" t="n">
-        <v>800000</v>
+        <v>1279000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-700000</v>
+        <v>-1397000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-100000</v>
+        <v>92000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-19800000</v>
+        <v>1093000</v>
       </c>
       <c r="AL3" t="n">
-        <v>7100000</v>
+        <v>3169000</v>
       </c>
       <c r="AM3" t="n">
-        <v>15300000</v>
+        <v>11844000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2600000</v>
+        <v>16106000</v>
       </c>
       <c r="AO3" t="n">
-        <v>4800000</v>
+        <v>4768000</v>
       </c>
       <c r="AP3" t="n">
-        <v>104800000</v>
+        <v>90590000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10800000</v>
+        <v>9026000</v>
       </c>
       <c r="AR3" t="n">
-        <v>34200000</v>
+        <v>29221000</v>
       </c>
       <c r="AS3" t="n">
-        <v>34200000</v>
+        <v>29221000</v>
       </c>
       <c r="AT3" t="n">
-        <v>13800000</v>
+        <v>9715000</v>
       </c>
       <c r="AU3" t="n">
-        <v>3300000</v>
+        <v>2723000</v>
       </c>
       <c r="AV3" t="n">
-        <v>10500000</v>
+        <v>6992000</v>
       </c>
       <c r="AW3" t="n">
-        <v>2800000</v>
+        <v>3699000</v>
       </c>
       <c r="AX3" t="n">
-        <v>109600000</v>
+        <v>95358000</v>
       </c>
       <c r="AY3" t="n">
-        <v>11900000</v>
+        <v>30813000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>121500000</v>
+        <v>126171000</v>
       </c>
       <c r="BA3" t="n">
-        <v>121500000</v>
+        <v>126171000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>2672100</v>
+        <v>288372.093023</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15</v>
+        <v>0.046512</v>
       </c>
       <c r="D4" t="n">
-        <v>47237000</v>
+        <v>34700000</v>
       </c>
       <c r="E4" t="n">
-        <v>17840000</v>
+        <v>6200000</v>
       </c>
       <c r="F4" t="n">
-        <v>17814000</v>
+        <v>6200000</v>
       </c>
       <c r="G4" t="n">
-        <v>14903000</v>
+        <v>-9600000</v>
       </c>
       <c r="H4" t="n">
-        <v>29371000</v>
+        <v>34200000</v>
       </c>
       <c r="I4" t="n">
-        <v>30813000</v>
+        <v>11900000</v>
       </c>
       <c r="J4" t="n">
-        <v>65077000</v>
+        <v>40900000</v>
       </c>
       <c r="K4" t="n">
-        <v>35706000</v>
+        <v>6700000</v>
       </c>
       <c r="L4" t="n">
-        <v>1093000</v>
+        <v>-19800000</v>
       </c>
       <c r="M4" t="n">
-        <v>11844000</v>
+        <v>15300000</v>
       </c>
       <c r="N4" t="n">
-        <v>16106000</v>
+        <v>2600000</v>
       </c>
       <c r="O4" t="n">
-        <v>-212900</v>
+        <v>-15511627.906977</v>
       </c>
       <c r="P4" t="n">
-        <v>14903000</v>
+        <v>-9600000</v>
       </c>
       <c r="Q4" t="n">
-        <v>121403000</v>
+        <v>116700000</v>
       </c>
       <c r="R4" t="n">
-        <v>3699000</v>
+        <v>2800000</v>
       </c>
       <c r="S4" t="n">
-        <v>6173000</v>
+        <v>5700000</v>
       </c>
       <c r="T4" t="n">
-        <v>76337000</v>
+        <v>76300000</v>
       </c>
       <c r="U4" t="n">
-        <v>76337000</v>
+        <v>76300000</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="X4" t="n">
-        <v>14903000</v>
+        <v>-9600000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>14903000</v>
+        <v>-9600000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>14903000</v>
+        <v>-9600000</v>
       </c>
       <c r="AC4" t="n">
-        <v>809000</v>
+        <v>-1400000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14094000</v>
+        <v>-8200000</v>
       </c>
       <c r="AE4" t="n">
-        <v>14094000</v>
+        <v>-8200000</v>
       </c>
       <c r="AF4" t="n">
-        <v>9768000</v>
+        <v>-400000</v>
       </c>
       <c r="AG4" t="n">
-        <v>23862000</v>
+        <v>-8600000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1279000</v>
+        <v>800000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1397000</v>
+        <v>-700000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92000</v>
+        <v>-100000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1093000</v>
+        <v>-19800000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3169000</v>
+        <v>7100000</v>
       </c>
       <c r="AM4" t="n">
-        <v>11844000</v>
+        <v>15300000</v>
       </c>
       <c r="AN4" t="n">
-        <v>16106000</v>
+        <v>2600000</v>
       </c>
       <c r="AO4" t="n">
-        <v>4768000</v>
+        <v>4800000</v>
       </c>
       <c r="AP4" t="n">
-        <v>90590000</v>
+        <v>104800000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9026000</v>
+        <v>10800000</v>
       </c>
       <c r="AR4" t="n">
-        <v>29221000</v>
+        <v>34200000</v>
       </c>
       <c r="AS4" t="n">
-        <v>29221000</v>
+        <v>34200000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9715000</v>
+        <v>13800000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2723000</v>
+        <v>3300000</v>
       </c>
       <c r="AV4" t="n">
-        <v>6992000</v>
+        <v>10500000</v>
       </c>
       <c r="AW4" t="n">
-        <v>3699000</v>
+        <v>2800000</v>
       </c>
       <c r="AX4" t="n">
-        <v>95358000</v>
+        <v>109600000</v>
       </c>
       <c r="AY4" t="n">
-        <v>30813000</v>
+        <v>11900000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>126171000</v>
+        <v>121500000</v>
       </c>
       <c r="BA4" t="n">
-        <v>126171000</v>
+        <v>121500000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>929100</v>
+        <v>-75000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>32377000</v>
+        <v>70400000</v>
       </c>
       <c r="E5" t="n">
-        <v>3123000</v>
+        <v>-500000</v>
       </c>
       <c r="F5" t="n">
-        <v>3097000</v>
+        <v>-500000</v>
       </c>
       <c r="G5" t="n">
-        <v>25127000</v>
+        <v>-4400000</v>
       </c>
       <c r="H5" t="n">
-        <v>23415000</v>
+        <v>34300000</v>
       </c>
       <c r="I5" t="n">
-        <v>36159000</v>
+        <v>55400000</v>
       </c>
       <c r="J5" t="n">
-        <v>35500000</v>
+        <v>69900000</v>
       </c>
       <c r="K5" t="n">
-        <v>12085000</v>
+        <v>35300000</v>
       </c>
       <c r="L5" t="n">
-        <v>-9015000</v>
+        <v>-21700000</v>
       </c>
       <c r="M5" t="n">
-        <v>9057000</v>
+        <v>25200000</v>
       </c>
       <c r="N5" t="n">
-        <v>884000</v>
+        <v>2800000</v>
       </c>
       <c r="O5" t="n">
-        <v>22985100</v>
+        <v>-3975000</v>
       </c>
       <c r="P5" t="n">
-        <v>25127000</v>
+        <v>-4400000</v>
       </c>
       <c r="Q5" t="n">
-        <v>108921000</v>
+        <v>176200000</v>
       </c>
       <c r="R5" t="n">
-        <v>1203000</v>
+        <v>2600000</v>
       </c>
       <c r="S5" t="n">
-        <v>9265000</v>
+        <v>34400000</v>
       </c>
       <c r="T5" t="n">
-        <v>76337000</v>
+        <v>76500000</v>
       </c>
       <c r="U5" t="n">
-        <v>76337000</v>
+        <v>76500000</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="X5" t="n">
-        <v>25127000</v>
+        <v>-4400000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>25127000</v>
+        <v>-4400000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>25127000</v>
+        <v>-4400000</v>
       </c>
       <c r="AC5" t="n">
-        <v>463000</v>
+        <v>-700000</v>
       </c>
       <c r="AD5" t="n">
-        <v>24664000</v>
+        <v>-3800000</v>
       </c>
       <c r="AE5" t="n">
-        <v>24664000</v>
+        <v>-3800000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-21636000</v>
+        <v>13800000</v>
       </c>
       <c r="AG5" t="n">
-        <v>3028000</v>
+        <v>10100000</v>
       </c>
       <c r="AH5" t="n">
-        <v>458000</v>
+        <v>1500000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-410000</v>
+        <v>-1500000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-74000</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-9015000</v>
+        <v>-21700000</v>
       </c>
       <c r="AL5" t="n">
-        <v>842000</v>
+        <v>-700000</v>
       </c>
       <c r="AM5" t="n">
-        <v>9057000</v>
+        <v>25200000</v>
       </c>
       <c r="AN5" t="n">
-        <v>884000</v>
+        <v>2800000</v>
       </c>
       <c r="AO5" t="n">
-        <v>8807000</v>
+        <v>34200000</v>
       </c>
       <c r="AP5" t="n">
-        <v>72762000</v>
+        <v>120800000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5192000</v>
+        <v>12500000</v>
       </c>
       <c r="AR5" t="n">
-        <v>23389000</v>
+        <v>34600000</v>
       </c>
       <c r="AS5" t="n">
-        <v>23389000</v>
+        <v>34600000</v>
       </c>
       <c r="AT5" t="n">
-        <v>7726000</v>
+        <v>15200000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1622000</v>
+        <v>4300000</v>
       </c>
       <c r="AV5" t="n">
-        <v>6104000</v>
+        <v>10900000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1203000</v>
+        <v>2600000</v>
       </c>
       <c r="AX5" t="n">
-        <v>81569000</v>
+        <v>155000000</v>
       </c>
       <c r="AY5" t="n">
-        <v>36159000</v>
+        <v>55400000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>117728000</v>
+        <v>210400000</v>
       </c>
       <c r="BA5" t="n">
-        <v>117728000</v>
+        <v>210400000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-2130000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>63200000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-14200000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-14200000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-43100000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>41100000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>57300000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-33200000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24600000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-31030000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-43100000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>200100000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12900000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>76600000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>76600000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-43100000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-43100000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-43100000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-47400000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-47400000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-18100000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-17100000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>17100000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-33200000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>13700000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>24600000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>30100000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>142800000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16700000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>20100000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>172900000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>57300000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>230200000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>230200000</v>
       </c>
     </row>
   </sheetData>
@@ -1340,7 +1501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,214 +1840,96 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>76603334</v>
-      </c>
-      <c r="D2" t="n">
-        <v>76603334</v>
-      </c>
-      <c r="E2" t="n">
-        <v>652100000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>893200000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>132400000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>941200000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>285000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>132400000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>149500000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>197500000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>869400000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>194700000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-2800000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>197500000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>45500000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>86300000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>76600000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>76600000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1069000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>842300000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-200000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>21700000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>813800000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>141900000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>671900000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>226700000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>40700000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>79400000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>7600000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>71800000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>75600000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>700000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>73700000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1263700000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>752000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>79000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>65100000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>700000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>64400000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>591600000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-178800000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>770400000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>33700000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>130400000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>583900000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>22400000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>511700000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>14500000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>116400000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>172000000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>169300000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>22800000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>10800000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>83600000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>91600000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>91600000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>266803</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>266803</v>
@@ -1898,201 +1941,203 @@
         <v>76603334</v>
       </c>
       <c r="E3" t="n">
-        <v>512400000</v>
+        <v>331376000</v>
       </c>
       <c r="F3" t="n">
-        <v>766400000</v>
+        <v>569968000</v>
       </c>
       <c r="G3" t="n">
-        <v>146700000</v>
+        <v>172892000</v>
       </c>
       <c r="H3" t="n">
-        <v>814400000</v>
+        <v>690708000</v>
       </c>
       <c r="I3" t="n">
-        <v>288100000</v>
+        <v>194984000</v>
       </c>
       <c r="J3" t="n">
-        <v>146700000</v>
+        <v>172892000</v>
       </c>
       <c r="K3" t="n">
-        <v>163600000</v>
+        <v>117010000</v>
       </c>
       <c r="L3" t="n">
-        <v>211600000</v>
+        <v>237750000</v>
       </c>
       <c r="M3" t="n">
-        <v>760700000</v>
+        <v>655352000</v>
       </c>
       <c r="N3" t="n">
-        <v>208200000</v>
+        <v>232160000</v>
       </c>
       <c r="O3" t="n">
-        <v>-3400000</v>
+        <v>-5590000</v>
       </c>
       <c r="P3" t="n">
-        <v>211600000</v>
+        <v>237750000</v>
       </c>
       <c r="Q3" t="n">
-        <v>700000</v>
+        <v>707000</v>
       </c>
       <c r="R3" t="n">
-        <v>65600000</v>
+        <v>81932000</v>
       </c>
       <c r="S3" t="n">
-        <v>83000000</v>
+        <v>82953000</v>
       </c>
       <c r="T3" t="n">
-        <v>76600000</v>
+        <v>76603000</v>
       </c>
       <c r="U3" t="n">
-        <v>76600000</v>
+        <v>76603000</v>
       </c>
       <c r="V3" t="n">
-        <v>893500000</v>
+        <v>688176000</v>
       </c>
       <c r="W3" t="n">
-        <v>731500000</v>
+        <v>548327000</v>
       </c>
       <c r="X3" t="n">
-        <v>-1001000</v>
+        <v>3000</v>
       </c>
       <c r="Y3" t="n">
-        <v>600000</v>
+        <v>620000</v>
       </c>
       <c r="Z3" t="n">
-        <v>18000000</v>
+        <v>17134000</v>
       </c>
       <c r="AA3" t="n">
-        <v>705200000</v>
+        <v>528809000</v>
       </c>
       <c r="AB3" t="n">
-        <v>156100000</v>
+        <v>111207000</v>
       </c>
       <c r="AC3" t="n">
-        <v>549100000</v>
+        <v>417602000</v>
       </c>
       <c r="AD3" t="n">
-        <v>162000000</v>
+        <v>139849000</v>
       </c>
       <c r="AE3" t="n">
-        <v>13500000</v>
+        <v>13654000</v>
       </c>
       <c r="AF3" t="n">
-        <v>6600000</v>
+        <v>3782000</v>
       </c>
       <c r="AG3" t="n">
-        <v>61200000</v>
+        <v>41159000</v>
       </c>
       <c r="AH3" t="n">
-        <v>7500000</v>
+        <v>5803000</v>
       </c>
       <c r="AI3" t="n">
-        <v>53700000</v>
+        <v>35356000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6400000</v>
+        <v>6047000</v>
       </c>
       <c r="AK3" t="n">
-        <v>60900000</v>
+        <v>45581000</v>
       </c>
       <c r="AL3" t="n">
-        <v>900000</v>
+        <v>979000</v>
       </c>
       <c r="AM3" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="AN3" t="n">
-        <v>59700000</v>
+        <v>44572000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1101700000</v>
+        <v>920336000</v>
       </c>
       <c r="AP3" t="n">
-        <v>651700000</v>
+        <v>585502000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>78000000</v>
+        <v>65309000</v>
       </c>
       <c r="AR3" t="n">
-        <v>3600000</v>
+        <v>1793000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1200000</v>
+        <v>1278000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2400000</v>
+        <v>515000</v>
       </c>
       <c r="AU3" t="n">
-        <v>64900000</v>
+        <v>64858000</v>
       </c>
       <c r="AV3" t="n">
-        <v>500000</v>
+        <v>462000</v>
       </c>
       <c r="AW3" t="n">
-        <v>64400000</v>
+        <v>64396000</v>
       </c>
       <c r="AX3" t="n">
-        <v>491300000</v>
+        <v>441132000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-150000000</v>
+        <v>-119668000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>641300000</v>
+        <v>560800000</v>
       </c>
       <c r="BA3" t="n">
-        <v>13900000</v>
+        <v>10185000</v>
       </c>
       <c r="BB3" t="n">
-        <v>117800000</v>
+        <v>105542000</v>
       </c>
       <c r="BC3" t="n">
-        <v>487300000</v>
+        <v>423073000</v>
       </c>
       <c r="BD3" t="n">
-        <v>22300000</v>
+        <v>22000000</v>
       </c>
       <c r="BE3" t="n">
-        <v>450100000</v>
+        <v>334833000</v>
       </c>
       <c r="BF3" t="n">
-        <v>20400000</v>
+        <v>15751000</v>
       </c>
       <c r="BG3" t="n">
-        <v>90500000</v>
+        <v>37001000</v>
       </c>
       <c r="BH3" t="n">
-        <v>190800000</v>
+        <v>110370000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>190500000</v>
+        <v>110083000</v>
       </c>
       <c r="BK3" t="n">
-        <v>300000</v>
+        <v>285000</v>
       </c>
       <c r="BL3" t="n">
-        <v>14800000</v>
+        <v>9984000</v>
       </c>
       <c r="BM3" t="n">
-        <v>5400000</v>
+        <v>1993000</v>
       </c>
       <c r="BN3" t="n">
-        <v>37800000</v>
+        <v>38152000</v>
       </c>
       <c r="BO3" t="n">
-        <v>90400000</v>
+        <v>121582000</v>
       </c>
       <c r="BP3" t="n">
-        <v>90400000</v>
-      </c>
+        <v>121582000</v>
+      </c>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>266803</v>
@@ -2104,402 +2149,618 @@
         <v>76603334</v>
       </c>
       <c r="E4" t="n">
-        <v>331376000</v>
+        <v>526500000</v>
       </c>
       <c r="F4" t="n">
-        <v>569968000</v>
+        <v>780500000</v>
       </c>
       <c r="G4" t="n">
-        <v>172892000</v>
+        <v>137700000</v>
       </c>
       <c r="H4" t="n">
-        <v>690708000</v>
+        <v>819500000</v>
       </c>
       <c r="I4" t="n">
-        <v>194984000</v>
+        <v>294200000</v>
       </c>
       <c r="J4" t="n">
-        <v>172892000</v>
+        <v>137700000</v>
       </c>
       <c r="K4" t="n">
-        <v>117010000</v>
+        <v>163600000</v>
       </c>
       <c r="L4" t="n">
-        <v>237750000</v>
+        <v>202600000</v>
       </c>
       <c r="M4" t="n">
-        <v>655352000</v>
+        <v>771500000</v>
       </c>
       <c r="N4" t="n">
-        <v>232160000</v>
+        <v>199200000</v>
       </c>
       <c r="O4" t="n">
-        <v>-5590000</v>
+        <v>-3400000</v>
       </c>
       <c r="P4" t="n">
-        <v>237750000</v>
+        <v>202600000</v>
       </c>
       <c r="Q4" t="n">
-        <v>707000</v>
+        <v>700000</v>
       </c>
       <c r="R4" t="n">
-        <v>81932000</v>
+        <v>56500000</v>
       </c>
       <c r="S4" t="n">
-        <v>82953000</v>
+        <v>83000000</v>
       </c>
       <c r="T4" t="n">
-        <v>76603000</v>
+        <v>76600000</v>
       </c>
       <c r="U4" t="n">
-        <v>76603000</v>
+        <v>76600000</v>
       </c>
       <c r="V4" t="n">
-        <v>688176000</v>
+        <v>904600000</v>
       </c>
       <c r="W4" t="n">
-        <v>548327000</v>
+        <v>748400000</v>
       </c>
       <c r="X4" t="n">
-        <v>3000</v>
+        <v>-1001000</v>
       </c>
       <c r="Y4" t="n">
-        <v>620000</v>
+        <v>600000</v>
       </c>
       <c r="Z4" t="n">
-        <v>17134000</v>
+        <v>15100000</v>
       </c>
       <c r="AA4" t="n">
-        <v>528809000</v>
+        <v>725000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>111207000</v>
+        <v>156100000</v>
       </c>
       <c r="AC4" t="n">
-        <v>417602000</v>
+        <v>568900000</v>
       </c>
       <c r="AD4" t="n">
-        <v>139849000</v>
+        <v>156200000</v>
       </c>
       <c r="AE4" t="n">
-        <v>13654000</v>
+        <v>13500000</v>
       </c>
       <c r="AF4" t="n">
-        <v>3782000</v>
+        <v>6600000</v>
       </c>
       <c r="AG4" t="n">
-        <v>41159000</v>
+        <v>55500000</v>
       </c>
       <c r="AH4" t="n">
-        <v>5803000</v>
+        <v>7500000</v>
       </c>
       <c r="AI4" t="n">
-        <v>35356000</v>
+        <v>48000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6047000</v>
+        <v>6400000</v>
       </c>
       <c r="AK4" t="n">
-        <v>45581000</v>
+        <v>60800000</v>
       </c>
       <c r="AL4" t="n">
-        <v>979000</v>
+        <v>800000</v>
       </c>
       <c r="AM4" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="AN4" t="n">
-        <v>44572000</v>
+        <v>59700000</v>
       </c>
       <c r="AO4" t="n">
-        <v>920336000</v>
+        <v>1103800000</v>
       </c>
       <c r="AP4" t="n">
-        <v>585502000</v>
+        <v>653400000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>65309000</v>
+        <v>79000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1793000</v>
+        <v>3600000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1278000</v>
+        <v>1200000</v>
       </c>
       <c r="AT4" t="n">
-        <v>515000</v>
+        <v>2400000</v>
       </c>
       <c r="AU4" t="n">
-        <v>64858000</v>
+        <v>64900000</v>
       </c>
       <c r="AV4" t="n">
-        <v>462000</v>
+        <v>500000</v>
       </c>
       <c r="AW4" t="n">
-        <v>64396000</v>
+        <v>64400000</v>
       </c>
       <c r="AX4" t="n">
-        <v>441132000</v>
+        <v>491300000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-119668000</v>
+        <v>-150000000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>560800000</v>
+        <v>641300000</v>
       </c>
       <c r="BA4" t="n">
-        <v>10185000</v>
+        <v>13900000</v>
       </c>
       <c r="BB4" t="n">
-        <v>105542000</v>
+        <v>117800000</v>
       </c>
       <c r="BC4" t="n">
-        <v>423073000</v>
+        <v>487300000</v>
       </c>
       <c r="BD4" t="n">
-        <v>22000000</v>
+        <v>22300000</v>
       </c>
       <c r="BE4" t="n">
-        <v>334833000</v>
+        <v>450400000</v>
       </c>
       <c r="BF4" t="n">
-        <v>15751000</v>
+        <v>20400000</v>
       </c>
       <c r="BG4" t="n">
-        <v>37001000</v>
+        <v>90500000</v>
       </c>
       <c r="BH4" t="n">
-        <v>110370000</v>
+        <v>281600000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>110083000</v>
+        <v>190500000</v>
       </c>
       <c r="BK4" t="n">
-        <v>285000</v>
+        <v>300000</v>
       </c>
       <c r="BL4" t="n">
-        <v>9984000</v>
+        <v>14800000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1993000</v>
+        <v>5400000</v>
       </c>
       <c r="BN4" t="n">
-        <v>38152000</v>
+        <v>37800000</v>
       </c>
       <c r="BO4" t="n">
-        <v>121582000</v>
+        <v>90400000</v>
       </c>
       <c r="BP4" t="n">
-        <v>121582000</v>
+        <v>90400000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="n">
-        <v>266803</v>
-      </c>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>76336531</v>
+        <v>76603334</v>
       </c>
       <c r="D5" t="n">
         <v>76603334</v>
       </c>
       <c r="E5" t="n">
-        <v>251649000</v>
+        <v>652000000</v>
       </c>
       <c r="F5" t="n">
-        <v>511855000</v>
+        <v>893100000</v>
       </c>
       <c r="G5" t="n">
-        <v>165211000</v>
+        <v>132400000</v>
       </c>
       <c r="H5" t="n">
-        <v>630449000</v>
+        <v>941100000</v>
       </c>
       <c r="I5" t="n">
-        <v>254165000</v>
+        <v>296700000</v>
       </c>
       <c r="J5" t="n">
-        <v>165211000</v>
+        <v>132400000</v>
       </c>
       <c r="K5" t="n">
-        <v>110581000</v>
+        <v>149500000</v>
       </c>
       <c r="L5" t="n">
-        <v>229175000</v>
+        <v>197500000</v>
       </c>
       <c r="M5" t="n">
-        <v>609117000</v>
+        <v>881200000</v>
       </c>
       <c r="N5" t="n">
-        <v>221793000</v>
+        <v>194700000</v>
       </c>
       <c r="O5" t="n">
-        <v>-7382000</v>
+        <v>-2800000</v>
       </c>
       <c r="P5" t="n">
-        <v>229175000</v>
+        <v>197500000</v>
       </c>
       <c r="Q5" t="n">
-        <v>707000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>73430000</v>
+        <v>45400000</v>
       </c>
       <c r="S5" t="n">
-        <v>82953000</v>
+        <v>86300000</v>
       </c>
       <c r="T5" t="n">
-        <v>76603000</v>
+        <v>76600000</v>
       </c>
       <c r="U5" t="n">
-        <v>76603000</v>
+        <v>76600000</v>
       </c>
       <c r="V5" t="n">
-        <v>605207000</v>
+        <v>1067400000</v>
       </c>
       <c r="W5" t="n">
-        <v>495903000</v>
+        <v>852600000</v>
       </c>
       <c r="X5" t="n">
-        <v>-3000</v>
+        <v>-200000</v>
       </c>
       <c r="Y5" t="n">
-        <v>667000</v>
+        <v>500000</v>
       </c>
       <c r="Z5" t="n">
-        <v>6454000</v>
+        <v>20200000</v>
       </c>
       <c r="AA5" t="n">
-        <v>483661000</v>
+        <v>825600000</v>
       </c>
       <c r="AB5" t="n">
-        <v>103719000</v>
+        <v>141900000</v>
       </c>
       <c r="AC5" t="n">
-        <v>379942000</v>
+        <v>683700000</v>
       </c>
       <c r="AD5" t="n">
-        <v>109304000</v>
+        <v>214800000</v>
       </c>
       <c r="AE5" t="n">
-        <v>12099000</v>
+        <v>40700000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1549000</v>
+        <v>4400000</v>
       </c>
       <c r="AG5" t="n">
-        <v>28194000</v>
+        <v>67500000</v>
       </c>
       <c r="AH5" t="n">
-        <v>6862000</v>
+        <v>7600000</v>
       </c>
       <c r="AI5" t="n">
-        <v>21332000</v>
+        <v>59900000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5198000</v>
+        <v>7000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>35649000</v>
+        <v>75600000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1213000</v>
+        <v>700000</v>
       </c>
       <c r="AM5" t="n">
-        <v>38000</v>
+        <v>1200000</v>
       </c>
       <c r="AN5" t="n">
-        <v>34398000</v>
+        <v>73700000</v>
       </c>
       <c r="AO5" t="n">
-        <v>827000000</v>
+        <v>1262100000</v>
       </c>
       <c r="AP5" t="n">
-        <v>463530000</v>
+        <v>750500000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>58713000</v>
+        <v>77500000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1911000</v>
+        <v>3700000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1450000</v>
+        <v>1900000</v>
       </c>
       <c r="AT5" t="n">
-        <v>461000</v>
+        <v>1800000</v>
       </c>
       <c r="AU5" t="n">
-        <v>63964000</v>
+        <v>65100000</v>
       </c>
       <c r="AV5" t="n">
-        <v>689000</v>
+        <v>700000</v>
       </c>
       <c r="AW5" t="n">
-        <v>63275000</v>
+        <v>64400000</v>
       </c>
       <c r="AX5" t="n">
-        <v>338255000</v>
+        <v>591600000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-92539000</v>
+        <v>-179400000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>430794000</v>
+        <v>771000000</v>
       </c>
       <c r="BA5" t="n">
-        <v>2502000</v>
+        <v>33700000</v>
       </c>
       <c r="BB5" t="n">
-        <v>76631000</v>
+        <v>130400000</v>
       </c>
       <c r="BC5" t="n">
-        <v>330304000</v>
+        <v>584500000</v>
       </c>
       <c r="BD5" t="n">
-        <v>21357000</v>
+        <v>22400000</v>
       </c>
       <c r="BE5" t="n">
-        <v>363469000</v>
+        <v>511500000</v>
       </c>
       <c r="BF5" t="n">
-        <v>12595000</v>
+        <v>14500000</v>
       </c>
       <c r="BG5" t="n">
-        <v>40891000</v>
+        <v>116400000</v>
       </c>
       <c r="BH5" t="n">
-        <v>122820000</v>
+        <v>171800000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2000</v>
+        <v>2700000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>122529000</v>
+        <v>169100000</v>
       </c>
       <c r="BK5" t="n">
-        <v>289000</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>7366000</v>
+        <v>22800000</v>
       </c>
       <c r="BM5" t="n">
-        <v>680000</v>
+        <v>10800000</v>
       </c>
       <c r="BN5" t="n">
-        <v>29492000</v>
+        <v>83600000</v>
       </c>
       <c r="BO5" t="n">
-        <v>149625000</v>
+        <v>91600000</v>
       </c>
       <c r="BP5" t="n">
-        <v>149625000</v>
+        <v>91600000</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>76603334</v>
+      </c>
+      <c r="D6" t="n">
+        <v>76603334</v>
+      </c>
+      <c r="E6" t="n">
+        <v>598200000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>808700000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>89400000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>832100000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>103100000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>89400000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>132400000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>155800000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>773200000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>154200000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1600000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>155800000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-3800000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>86300000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>76600000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>76600000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1027300000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>758300000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20600000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>737100000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>119700000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>617400000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>269000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>71600000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>58900000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>67400000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1181500000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>809500000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>54500000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>66400000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>64400000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>665100000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-214700000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>879800000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>13400000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>140800000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>703000000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22600000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>372100000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>16400000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>121800000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>10400000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>53100000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>78100000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>78100000</v>
+      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="n">
+        <v>60100000</v>
       </c>
     </row>
   </sheetData>
@@ -2513,7 +2774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2757,230 +3018,154 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Net Common Stock Issuance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-211300000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-46300000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>286600000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-34700000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>91600000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-13400000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>90400000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>220800000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-4300000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-6100000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>240300000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>240300000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-46300000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>286600000</v>
-      </c>
+        <v>-15754000</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>-3053000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>-21520000</v>
+      </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>-29600000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4700000</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-33500000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-34700000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-176600000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-8800000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-11500000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-149100000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>131100000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-240600000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-38000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>38200000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9300000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>31400000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>31400000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-75800000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-12700000</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-191700000</v>
+        <v>-104648000</v>
       </c>
       <c r="C3" t="n">
-        <v>-25200000</v>
+        <v>-71717000</v>
       </c>
       <c r="D3" t="n">
-        <v>197000000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+        <v>166167000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-25500000</v>
+        <v>-95637000</v>
       </c>
       <c r="G3" t="n">
-        <v>90400000</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>121582000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-153000</v>
+      </c>
       <c r="I3" t="n">
-        <v>121600000</v>
+        <v>149625000</v>
       </c>
       <c r="J3" t="n">
-        <v>-31200000</v>
+        <v>-27890000</v>
       </c>
       <c r="K3" t="n">
-        <v>155100000</v>
+        <v>79201000</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-6100000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>-6107000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-6107000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>171800000</v>
+        <v>94450000</v>
       </c>
       <c r="Q3" t="n">
-        <v>171800000</v>
+        <v>89450000</v>
       </c>
       <c r="R3" t="n">
-        <v>-25200000</v>
+        <v>-21717000</v>
       </c>
       <c r="S3" t="n">
-        <v>197000000</v>
+        <v>111167000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-50000000</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>55000000</v>
       </c>
       <c r="W3" t="n">
-        <v>-20100000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>100000</v>
-      </c>
+        <v>-98080000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-2100000</v>
+        <v>-455000</v>
       </c>
       <c r="Z3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2200000</v>
+        <v>-455000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4800000</v>
+        <v>-2000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>4800000</v>
+        <v>3000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-2003000</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -2989,139 +3174,142 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-22900000</v>
+        <v>-95625000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2600000</v>
+        <v>12000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-25500000</v>
+        <v>-95637000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-166200000</v>
+        <v>-9011000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-3500000</v>
+        <v>-5678000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2000000</v>
+        <v>642000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-11100000</v>
+        <v>-8867000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-188800000</v>
+        <v>-30780000</v>
       </c>
       <c r="AO3" t="n">
-        <v>26100000</v>
+        <v>-14968000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-232600000</v>
+        <v>-39170000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14600000</v>
+        <v>20248000</v>
       </c>
       <c r="AR3" t="n">
-        <v>15200000</v>
+        <v>-17564000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-900000</v>
+        <v>9627000</v>
       </c>
       <c r="AT3" t="n">
-        <v>34200000</v>
+        <v>29371000</v>
       </c>
       <c r="AU3" t="n">
-        <v>34200000</v>
+        <v>29371000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-5000000</v>
+        <v>145000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-8200000</v>
-      </c>
+        <v>14094000</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-104648000</v>
+        <v>-191700000</v>
       </c>
       <c r="C4" t="n">
-        <v>-71717000</v>
+        <v>-25200000</v>
       </c>
       <c r="D4" t="n">
-        <v>166167000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>197000000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-95637000</v>
+        <v>-25500000</v>
       </c>
       <c r="G4" t="n">
-        <v>121582000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-153000</v>
-      </c>
+        <v>90400000</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>149625000</v>
+        <v>121600000</v>
       </c>
       <c r="J4" t="n">
-        <v>-27890000</v>
+        <v>-31200000</v>
       </c>
       <c r="K4" t="n">
-        <v>79201000</v>
+        <v>155100000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-6107000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-6107000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>-6100000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>94450000</v>
+        <v>171800000</v>
       </c>
       <c r="Q4" t="n">
-        <v>89450000</v>
+        <v>171800000</v>
       </c>
       <c r="R4" t="n">
-        <v>-21717000</v>
+        <v>-25200000</v>
       </c>
       <c r="S4" t="n">
-        <v>111167000</v>
+        <v>197000000</v>
       </c>
       <c r="T4" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-50000000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>55000000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-98080000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>-20100000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>100000</v>
+      </c>
       <c r="Y4" t="n">
-        <v>-455000</v>
+        <v>-2100000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-455000</v>
+        <v>-2200000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2000000</v>
+        <v>4800000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3000</v>
+        <v>4800000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2003000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -3130,190 +3318,348 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-95625000</v>
+        <v>-22900000</v>
       </c>
       <c r="AH4" t="n">
-        <v>12000</v>
+        <v>2600000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-95637000</v>
+        <v>-25500000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-9011000</v>
+        <v>-166200000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5678000</v>
+        <v>-3500000</v>
       </c>
       <c r="AL4" t="n">
-        <v>642000</v>
+        <v>2000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-8867000</v>
+        <v>-11100000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-30780000</v>
+        <v>-188800000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-14968000</v>
+        <v>26100000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-39170000</v>
+        <v>-232600000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20248000</v>
+        <v>14600000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-17564000</v>
+        <v>15200000</v>
       </c>
       <c r="AS4" t="n">
-        <v>9627000</v>
+        <v>-900000</v>
       </c>
       <c r="AT4" t="n">
-        <v>29371000</v>
+        <v>34200000</v>
       </c>
       <c r="AU4" t="n">
-        <v>29371000</v>
+        <v>34200000</v>
       </c>
       <c r="AV4" t="n">
-        <v>145000</v>
+        <v>-5000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>14094000</v>
-      </c>
+        <v>-8200000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-89050000</v>
+        <v>-211300000</v>
       </c>
       <c r="C5" t="n">
-        <v>-21520000</v>
+        <v>-46300000</v>
       </c>
       <c r="D5" t="n">
-        <v>143699000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>286600000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3600000</v>
+      </c>
       <c r="F5" t="n">
-        <v>-112828000</v>
+        <v>-34700000</v>
       </c>
       <c r="G5" t="n">
-        <v>149625000</v>
+        <v>91600000</v>
       </c>
       <c r="H5" t="n">
-        <v>-15754000</v>
+        <v>-13500000</v>
       </c>
       <c r="I5" t="n">
-        <v>111618000</v>
+        <v>90400000</v>
       </c>
       <c r="J5" t="n">
-        <v>53761000</v>
+        <v>14700000</v>
       </c>
       <c r="K5" t="n">
-        <v>111974000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>220800000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-4300000</v>
+      </c>
       <c r="M5" t="n">
-        <v>-3053000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-3053000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>-6100000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>3600000</v>
+      </c>
       <c r="P5" t="n">
-        <v>122179000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+        <v>240300000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>240300000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-46300000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>286600000</v>
+      </c>
       <c r="T5" t="n">
-        <v>122179000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-21520000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>143699000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-81991000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>-29500000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-100000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>-136000</v>
+        <v>-700000</v>
       </c>
       <c r="Z5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-139000</v>
+        <v>-700000</v>
       </c>
       <c r="AB5" t="n">
-        <v>30447000</v>
+        <v>4700000</v>
       </c>
       <c r="AC5" t="n">
-        <v>30447000</v>
+        <v>4700000</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-112303000</v>
+        <v>-33500000</v>
       </c>
       <c r="AH5" t="n">
-        <v>525000</v>
+        <v>1200000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-112828000</v>
+        <v>-34700000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23778000</v>
+        <v>-176600000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-4918000</v>
+        <v>-8800000</v>
       </c>
       <c r="AL5" t="n">
-        <v>309000</v>
+        <v>2400000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-6556000</v>
+        <v>-11500000</v>
       </c>
       <c r="AN5" t="n">
-        <v>2436000</v>
+        <v>-150700000</v>
       </c>
       <c r="AO5" t="n">
-        <v>44052000</v>
+        <v>129500000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-85384000</v>
+        <v>-240600000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>41549000</v>
+        <v>-38000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>5849000</v>
+        <v>24200000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-21848000</v>
+        <v>13100000</v>
       </c>
       <c r="AT5" t="n">
-        <v>23415000</v>
+        <v>34300000</v>
       </c>
       <c r="AU5" t="n">
-        <v>23415000</v>
+        <v>34300000</v>
       </c>
       <c r="AV5" t="n">
-        <v>425000</v>
+        <v>-75800000</v>
       </c>
       <c r="AW5" t="n">
-        <v>24664000</v>
+        <v>-3800000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-153900000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-68900000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>171400000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-103900000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>78100000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1900000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>91600000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-11600000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>101400000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-6700000</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>102500000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>92500000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-68900000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>161400000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-63000000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12300000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-11300000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>39900000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>39900000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-103900000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-103900000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-50000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-6300000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-22000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-125100000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-17000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-103700000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-8300000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>100300000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>41100000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>41100000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-47400000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3327,7 +3673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL2"/>
+  <dimension ref="A1:EH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3473,570 +3819,550 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>shortName</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
       <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4053,10 +4379,8 @@
           <t>Cuxhaven</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>27472</t>
-        </is>
+      <c r="C2" t="n">
+        <v>27472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4114,11 +4438,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>681</v>
+        <v>666</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Harald  Wilbert', 'age': 58, 'title': 'CFO &amp; Member of Management Board', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 479000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Roland  Stanze', 'age': 60, 'title': 'COO &amp; Member of Management Board', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 400000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Dirk  Simons', 'age': 59, 'title': 'Member of Management Board', 'yearBorn': 1966, 'fiscalYear': 2024, 'totalPay': 11000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Heiko  Wuttke', 'age': 57, 'title': 'CEO &amp; Chairman of Management Board', 'yearBorn': 1968, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Christopher  Rodler', 'title': 'Head of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Alexander  Lennemann', 'title': 'Head of Corporate Communications', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Thorsten  Fastenau', 'title': 'Head of Offshore Wind', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Dirk  Simons', 'age': 59, 'title': 'CFO &amp; Member of Management Board', 'yearBorn': 1966, 'fiscalYear': 2024, 'totalPay': 11000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Roland  Stanze', 'age': 60, 'title': 'COO &amp; Member of Management Board', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 400000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Heiko  Wuttke', 'age': 57, 'title': 'CEO &amp; Chairman of Management Board', 'yearBorn': 1968, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Christopher  Rodler', 'title': 'Head of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Alexander  Lennemann', 'title': 'Head of Corporate Communications', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Thorsten  Fastenau', 'title': 'Head of Offshore Wind', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4136,411 +4460,399 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>10.1</v>
+        <v>10.98</v>
       </c>
       <c r="V2" t="n">
-        <v>10.46</v>
+        <v>11.52</v>
       </c>
       <c r="W2" t="n">
-        <v>10.18</v>
+        <v>11.4</v>
       </c>
       <c r="X2" t="n">
-        <v>10.46</v>
+        <v>11.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.1</v>
+        <v>10.98</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.46</v>
+        <v>11.52</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.18</v>
+        <v>11.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.46</v>
+        <v>11.52</v>
       </c>
       <c r="AC2" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1502</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1502</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>104</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>172</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>172</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>854893248</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>825783940</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.3071306</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9.640599999999999</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10.06385</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1544771968</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.14236</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12454394</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>76603334</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.93171996</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>76603334</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.650633</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-36800000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>5.976</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.28553134</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BP2" t="n">
         <v>0.04</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="BQ2" t="n">
         <v>1779235200</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>108</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>770629568</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>775225740</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.3476524</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.8148</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>10.30295</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BS2" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BU2" t="n">
+        <v>61200000</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>809699968</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>258500000</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>541.968</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.02508</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>-0.24134001</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>192100000</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>112687504</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>-43900000</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.74313</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-0.00712</v>
+      </c>
+      <c r="CM2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1494729600</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.18722999</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>12454936</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>76603334</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0.93144</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>76603334</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.034</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>4.94592</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-43100000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>6.493</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>-0.3397864</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1779235200</v>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BW2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="BY2" t="n">
-        <v>83700000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.093</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>69200000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>809400000</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1.384</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>230200000</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>524.903</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>3.005</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0.01888</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>-0.27171</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>172900000</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>117912496</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>-50000000</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>-0.337</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>0.75109</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0.30061</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.58068</v>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>1PNE.MI</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>1PNE.MI</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CS2" t="b">
+        <v>0</v>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>PNE</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="CW2" t="b">
-        <v>0</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
+        <v>1781880356</v>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>PRE</t>
-        </is>
-      </c>
-      <c r="CZ2" t="n">
-        <v>-0.3960392</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
+          <t>finmb_882991</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>7200000</v>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>finmb_882991</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1.6393472</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
         <v>1708070400000</v>
       </c>
-      <c r="DH2" t="n">
-        <v>-0.03999996</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>10.18 - 10.46</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DJ2" t="n">
+        <v>0.1800003</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>11.4 - 11.52</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
         <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>108</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>2.4000006</v>
-      </c>
       <c r="DM2" t="n">
-        <v>0.31331602</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>7.66 - 16.18</t>
-        </is>
+        <v>104</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>3.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>-6.12</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.37824473</v>
+        <v>0.45691907</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>7.66 - 15.62</t>
+        </is>
       </c>
       <c r="DQ2" t="n">
-        <v>-33.97864</v>
+        <v>-4.46</v>
       </c>
       <c r="DR2" t="n">
-        <v>1786635000</v>
+        <v>-0.28553137</v>
       </c>
       <c r="DS2" t="n">
-        <v>1786635000</v>
+        <v>-28.553135</v>
       </c>
       <c r="DT2" t="n">
         <v>1786635000</v>
       </c>
       <c r="DU2" t="n">
+        <v>1786635000</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1786635000</v>
+      </c>
+      <c r="DW2" t="n">
         <v>1746777600</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="DX2" t="n">
         <v>1746777600</v>
       </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1.2452002</v>
+      <c r="DY2" t="b">
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.14126244</v>
+        <v>-0.37</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.24294949</v>
+        <v>1.5193996</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.023580575</v>
+        <v>0.15760426</v>
       </c>
       <c r="EC2" t="n">
+        <v>1.0961494</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.10891949</v>
+      </c>
+      <c r="EE2" t="n">
         <v>20</v>
       </c>
-      <c r="ED2" t="n">
+      <c r="EF2" t="n">
         <v>15</v>
       </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>7200000</v>
-      </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>PNE</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>1779358505</v>
-      </c>
-      <c r="EL2" t="inlineStr"/>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
